--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022276</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022272</v>
       </c>
       <c r="B3" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022273</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022281</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022279</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126022280</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126022278</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126022277</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022276</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022272</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022273</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022281</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022279</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126022280</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126022278</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126022277</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022276</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022272</v>
       </c>
       <c r="B3" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022273</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022281</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022279</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126022280</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126022278</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126022277</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126022276</v>
+        <v>126367288</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426778</v>
+        <v>426871</v>
       </c>
       <c r="R2" t="n">
-        <v>6799706</v>
+        <v>6800134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126022272</v>
+        <v>126367607</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426778</v>
+        <v>426969</v>
       </c>
       <c r="R3" t="n">
-        <v>6799707</v>
+        <v>6800067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022273</v>
+        <v>126367628</v>
       </c>
       <c r="B4" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426760</v>
+        <v>426944</v>
       </c>
       <c r="R4" t="n">
-        <v>6799692</v>
+        <v>6800071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022281</v>
+        <v>126367690</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426747</v>
+        <v>426944</v>
       </c>
       <c r="R5" t="n">
-        <v>6799718</v>
+        <v>6800071</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1066,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126022279</v>
+        <v>126363419</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426702</v>
+        <v>426471</v>
       </c>
       <c r="R6" t="n">
-        <v>6799828</v>
+        <v>6799648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1178,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,19 +1208,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022280</v>
+        <v>126363493</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1191,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426740</v>
+        <v>426475</v>
       </c>
       <c r="R7" t="n">
-        <v>6799743</v>
+        <v>6799627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1285,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1245,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022278</v>
+        <v>126363538</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1288,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426859</v>
+        <v>426499</v>
       </c>
       <c r="R8" t="n">
-        <v>6799862</v>
+        <v>6799642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1392,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1342,19 +1422,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126022277</v>
+        <v>126363391</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1385,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426835</v>
+        <v>426469</v>
       </c>
       <c r="R9" t="n">
-        <v>6799747</v>
+        <v>6799636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1499,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1439,15 +1529,6813 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126363342</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>426429</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6799635</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126022276</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>426778</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6799706</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126022272</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>426778</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6799707</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126022273</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>426760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6799692</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126022281</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>426747</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6799718</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126364297</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75072</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>426654</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6799714</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126364904</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>426631</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6799602</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126365078</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>426657</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6799606</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126365181</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>426687</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6799599</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126363871</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75072</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>426618</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6799683</v>
+      </c>
+      <c r="S19" t="n">
+        <v>23</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126364460</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>426590</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6799619</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126364869</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>426638</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6799643</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126364417</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>426577</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6799608</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126364611</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>426613</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6799597</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126364814</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>426628</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6799650</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126364842</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>426643</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6799654</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126365310</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>426696</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6799616</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126365592</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58513</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>426594</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6799656</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126022279</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>426702</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6799828</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126022280</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>426740</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6799743</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126369226</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>426795</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6799834</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126366267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>426742</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6799734</v>
+      </c>
+      <c r="S31" t="n">
+        <v>17</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126368547</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>426811</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6799987</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126369220</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>426795</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6799834</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126368672</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>426807</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6799965</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126366191</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>426755</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6799784</v>
+      </c>
+      <c r="S35" t="n">
+        <v>16</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126369239</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>426795</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6799834</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126364937</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>426794</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6799823</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126365001</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>426794</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6799824</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126365729</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>426740</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6799823</v>
+      </c>
+      <c r="S39" t="n">
+        <v>16</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126364974</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>426794</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6799824</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126365161</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>426764</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6799876</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126369140</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>426770</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6799835</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126368623</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>426819</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6799948</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126366027</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>426740</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6799823</v>
+      </c>
+      <c r="S44" t="n">
+        <v>12</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126368738</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>426799</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6799946</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126368886</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78978</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>426786</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6799905</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126369595</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>426797</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6799865</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126365589</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>426715</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6799803</v>
+      </c>
+      <c r="S48" t="n">
+        <v>13</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126366141</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>426755</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6799784</v>
+      </c>
+      <c r="S49" t="n">
+        <v>12</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126364655</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>426686</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6799727</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126369214</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>426795</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6799834</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126369047</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75072</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>426765</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6799867</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126368420</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58025</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>426822</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6800068</v>
+      </c>
+      <c r="S53" t="n">
+        <v>50</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126366000</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>426787</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6799803</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126365552</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>426713</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6799823</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126365510</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>426702</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6799810</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126365473</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>426701</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6799809</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126022278</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>426859</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6799862</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126022277</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>426835</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6799747</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126368288</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>426887</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6800029</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126369422</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126367203</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>426916</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6800140</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126368051</v>
+      </c>
+      <c r="B63" t="n">
+        <v>75072</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>426857</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6800079</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126368375</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>426857</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6800079</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126367784</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>426922</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6800077</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126369323</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126367410</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>426857</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6800108</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126367744</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>426922</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6800077</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126369415</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126367828</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>426882</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6800101</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126369426</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126369749</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>426870</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6799878</v>
+      </c>
+      <c r="S72" t="n">
+        <v>50</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126367862</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91262</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>426869</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6800102</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126364460</v>
+        <v>126364869</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426590</v>
+        <v>426638</v>
       </c>
       <c r="R20" t="n">
-        <v>6799619</v>
+        <v>6799643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126364869</v>
+        <v>126364460</v>
       </c>
       <c r="B21" t="n">
         <v>78977</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426638</v>
+        <v>426590</v>
       </c>
       <c r="R21" t="n">
-        <v>6799643</v>
+        <v>6799619</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126364814</v>
+        <v>126364842</v>
       </c>
       <c r="B24" t="n">
         <v>78977</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426628</v>
+        <v>426643</v>
       </c>
       <c r="R24" t="n">
-        <v>6799650</v>
+        <v>6799654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126364842</v>
+        <v>126365310</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426643</v>
+        <v>426696</v>
       </c>
       <c r="R25" t="n">
-        <v>6799654</v>
+        <v>6799616</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126365310</v>
+        <v>126364814</v>
       </c>
       <c r="B26" t="n">
         <v>78977</v>
@@ -3248,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426696</v>
+        <v>426628</v>
       </c>
       <c r="R26" t="n">
-        <v>6799616</v>
+        <v>6799650</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3283,7 +3288,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,12 +3298,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022279</v>
+        <v>126377439</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3443,37 +3443,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426702</v>
+        <v>426785</v>
       </c>
       <c r="R28" t="n">
-        <v>6799828</v>
+        <v>6799702</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3517,22 +3517,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126022280</v>
+        <v>126377460</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,37 +3540,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426740</v>
+        <v>426785</v>
       </c>
       <c r="R29" t="n">
-        <v>6799743</v>
+        <v>6799702</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3614,22 +3614,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126369226</v>
+        <v>126377488</v>
       </c>
       <c r="B30" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3637,37 +3637,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426795</v>
+        <v>426664</v>
       </c>
       <c r="R30" t="n">
-        <v>6799834</v>
+        <v>6799671</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3694,19 +3694,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,22 +3711,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126366267</v>
+        <v>126377440</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,37 +3734,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426742</v>
+        <v>426874</v>
       </c>
       <c r="R31" t="n">
-        <v>6799734</v>
+        <v>6799673</v>
       </c>
       <c r="S31" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3801,19 +3791,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3828,22 +3808,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126368547</v>
+        <v>126022279</v>
       </c>
       <c r="B32" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,34 +3831,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426811</v>
+        <v>426702</v>
       </c>
       <c r="R32" t="n">
-        <v>6799987</v>
+        <v>6799828</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3905,22 +3885,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3935,22 +3905,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126369220</v>
+        <v>126022280</v>
       </c>
       <c r="B33" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,34 +3928,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426795</v>
+        <v>426740</v>
       </c>
       <c r="R33" t="n">
-        <v>6799834</v>
+        <v>6799743</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4012,22 +3982,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4042,22 +4002,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126368672</v>
+        <v>126369226</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,21 +4025,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4049,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426807</v>
+        <v>426795</v>
       </c>
       <c r="R34" t="n">
-        <v>6799965</v>
+        <v>6799834</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,7 +4121,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126366191</v>
+        <v>126366267</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -4196,13 +4156,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426755</v>
+        <v>426742</v>
       </c>
       <c r="R35" t="n">
-        <v>6799784</v>
+        <v>6799734</v>
       </c>
       <c r="S35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4231,7 +4191,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4241,7 +4201,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,10 +4228,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126369239</v>
+        <v>126368547</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4279,21 +4239,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4303,10 +4263,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426795</v>
+        <v>426811</v>
       </c>
       <c r="R36" t="n">
-        <v>6799834</v>
+        <v>6799987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4375,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126364937</v>
+        <v>126369220</v>
       </c>
       <c r="B37" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4386,37 +4346,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426794</v>
+        <v>426795</v>
       </c>
       <c r="R37" t="n">
-        <v>6799823</v>
+        <v>6799834</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4445,7 +4405,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4455,7 +4415,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4470,22 +4430,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126365001</v>
+        <v>126368672</v>
       </c>
       <c r="B38" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4493,37 +4453,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426794</v>
+        <v>426807</v>
       </c>
       <c r="R38" t="n">
-        <v>6799824</v>
+        <v>6799965</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4552,7 +4512,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4562,7 +4522,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4577,22 +4537,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126365729</v>
+        <v>126369239</v>
       </c>
       <c r="B39" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4600,37 +4560,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426740</v>
+        <v>426795</v>
       </c>
       <c r="R39" t="n">
-        <v>6799823</v>
+        <v>6799834</v>
       </c>
       <c r="S39" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4659,7 +4619,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4669,7 +4629,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,22 +4644,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126364974</v>
+        <v>126366191</v>
       </c>
       <c r="B40" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,21 +4667,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,13 +4691,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426794</v>
+        <v>426755</v>
       </c>
       <c r="R40" t="n">
-        <v>6799824</v>
+        <v>6799784</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4766,7 +4726,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4776,7 +4736,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4791,44 +4751,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126365161</v>
+        <v>126364937</v>
       </c>
       <c r="B41" t="n">
-        <v>98269</v>
+        <v>78735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4838,10 +4798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426764</v>
+        <v>426794</v>
       </c>
       <c r="R41" t="n">
-        <v>6799876</v>
+        <v>6799823</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4873,7 +4833,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4883,7 +4843,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4910,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126369140</v>
+        <v>126365001</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4921,37 +4881,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426770</v>
+        <v>426794</v>
       </c>
       <c r="R42" t="n">
-        <v>6799835</v>
+        <v>6799824</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4980,7 +4940,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4990,7 +4950,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5005,19 +4965,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126368623</v>
+        <v>126369140</v>
       </c>
       <c r="B43" t="n">
         <v>78977</v>
@@ -5052,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426819</v>
+        <v>426770</v>
       </c>
       <c r="R43" t="n">
-        <v>6799948</v>
+        <v>6799835</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126366027</v>
+        <v>126364974</v>
       </c>
       <c r="B44" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5135,21 +5095,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,13 +5119,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426740</v>
+        <v>426794</v>
       </c>
       <c r="R44" t="n">
-        <v>6799823</v>
+        <v>6799824</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5194,7 +5154,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5204,7 +5164,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,19 +5179,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126368738</v>
+        <v>126368623</v>
       </c>
       <c r="B45" t="n">
         <v>78977</v>
@@ -5266,13 +5226,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426799</v>
+        <v>426819</v>
       </c>
       <c r="R45" t="n">
-        <v>6799946</v>
+        <v>6799948</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5338,10 +5298,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126368886</v>
+        <v>126365729</v>
       </c>
       <c r="B46" t="n">
-        <v>78978</v>
+        <v>79566</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,37 +5309,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426786</v>
+        <v>426740</v>
       </c>
       <c r="R46" t="n">
-        <v>6799905</v>
+        <v>6799823</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5408,7 +5368,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5418,12 +5378,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,60 +5393,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126369595</v>
+        <v>126365161</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>98269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426797</v>
+        <v>426764</v>
       </c>
       <c r="R47" t="n">
-        <v>6799865</v>
+        <v>6799876</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5520,7 +5475,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5530,7 +5485,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,22 +5500,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126365589</v>
+        <v>126368738</v>
       </c>
       <c r="B48" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,37 +5523,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426715</v>
+        <v>426799</v>
       </c>
       <c r="R48" t="n">
-        <v>6799803</v>
+        <v>6799946</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5627,7 +5582,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5637,7 +5592,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5652,19 +5607,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126366141</v>
+        <v>126366027</v>
       </c>
       <c r="B49" t="n">
         <v>79595</v>
@@ -5699,10 +5654,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426755</v>
+        <v>426740</v>
       </c>
       <c r="R49" t="n">
-        <v>6799784</v>
+        <v>6799823</v>
       </c>
       <c r="S49" t="n">
         <v>12</v>
@@ -5734,7 +5689,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5744,7 +5699,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5771,10 +5726,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126364655</v>
+        <v>126368886</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,16 +5737,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5802,17 +5757,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426686</v>
+        <v>426786</v>
       </c>
       <c r="R50" t="n">
-        <v>6799727</v>
+        <v>6799905</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5841,7 +5796,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5851,7 +5806,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5866,22 +5826,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126369214</v>
+        <v>126369595</v>
       </c>
       <c r="B51" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5889,21 +5849,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5873,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426795</v>
+        <v>426797</v>
       </c>
       <c r="R51" t="n">
-        <v>6799834</v>
+        <v>6799865</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5985,10 +5945,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126369047</v>
+        <v>126365589</v>
       </c>
       <c r="B52" t="n">
-        <v>75072</v>
+        <v>79595</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5956,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426765</v>
+        <v>426715</v>
       </c>
       <c r="R52" t="n">
-        <v>6799867</v>
+        <v>6799803</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6015,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,12 +6025,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6085,65 +6040,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126368420</v>
+        <v>126366141</v>
       </c>
       <c r="B53" t="n">
-        <v>58025</v>
+        <v>79595</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426822</v>
+        <v>426755</v>
       </c>
       <c r="R53" t="n">
-        <v>6800068</v>
+        <v>6799784</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6172,7 +6122,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6182,7 +6132,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6197,22 +6147,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126366000</v>
+        <v>126364655</v>
       </c>
       <c r="B54" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6220,21 +6170,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6244,10 +6194,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426787</v>
+        <v>426686</v>
       </c>
       <c r="R54" t="n">
-        <v>6799803</v>
+        <v>6799727</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6279,7 +6229,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6289,7 +6239,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6304,22 +6254,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126365552</v>
+        <v>126369214</v>
       </c>
       <c r="B55" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6327,37 +6277,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426713</v>
+        <v>426795</v>
       </c>
       <c r="R55" t="n">
-        <v>6799823</v>
+        <v>6799834</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6386,7 +6336,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6396,7 +6346,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6411,22 +6361,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126365510</v>
+        <v>126369047</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6434,37 +6384,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426702</v>
+        <v>426765</v>
       </c>
       <c r="R56" t="n">
-        <v>6799810</v>
+        <v>6799867</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6493,7 +6443,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6503,7 +6453,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6518,60 +6473,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126365473</v>
+        <v>126368420</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>58025</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426701</v>
+        <v>426822</v>
       </c>
       <c r="R57" t="n">
-        <v>6799809</v>
+        <v>6800068</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6600,7 +6560,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6610,7 +6570,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6625,22 +6585,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126022278</v>
+        <v>126366000</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,37 +6608,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426859</v>
+        <v>426787</v>
       </c>
       <c r="R58" t="n">
-        <v>6799862</v>
+        <v>6799803</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6702,12 +6662,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6722,22 +6692,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126022277</v>
+        <v>126365552</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6745,37 +6715,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426835</v>
+        <v>426713</v>
       </c>
       <c r="R59" t="n">
-        <v>6799747</v>
+        <v>6799823</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6799,12 +6769,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6819,19 +6799,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126368288</v>
+        <v>126365510</v>
       </c>
       <c r="B60" t="n">
         <v>78977</v>
@@ -6862,17 +6842,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426887</v>
+        <v>426702</v>
       </c>
       <c r="R60" t="n">
-        <v>6800029</v>
+        <v>6799810</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6901,7 +6881,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6911,7 +6891,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6926,22 +6906,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126369422</v>
+        <v>126365473</v>
       </c>
       <c r="B61" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6949,34 +6929,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426825</v>
+        <v>426701</v>
       </c>
       <c r="R61" t="n">
-        <v>6799839</v>
+        <v>6799809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7008,7 +6988,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7018,7 +6998,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7033,22 +7013,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126367203</v>
+        <v>126377418</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7056,37 +7036,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426916</v>
+        <v>426816</v>
       </c>
       <c r="R62" t="n">
-        <v>6800140</v>
+        <v>6799846</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7113,19 +7093,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7140,22 +7110,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126368051</v>
+        <v>126377462</v>
       </c>
       <c r="B63" t="n">
-        <v>75072</v>
+        <v>78735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7163,37 +7133,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426857</v>
+        <v>426794</v>
       </c>
       <c r="R63" t="n">
-        <v>6800079</v>
+        <v>6799832</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7220,19 +7190,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7247,19 +7207,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126368375</v>
+        <v>126377487</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -7290,17 +7250,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426857</v>
+        <v>426795</v>
       </c>
       <c r="R64" t="n">
-        <v>6800079</v>
+        <v>6799828</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7327,19 +7287,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7354,22 +7304,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126367784</v>
+        <v>126377441</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7377,37 +7327,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426922</v>
+        <v>426816</v>
       </c>
       <c r="R65" t="n">
-        <v>6800077</v>
+        <v>6799846</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7434,19 +7384,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7461,22 +7401,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126369323</v>
+        <v>126377461</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7484,37 +7424,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>426825</v>
+        <v>426816</v>
       </c>
       <c r="R66" t="n">
-        <v>6799839</v>
+        <v>6799846</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7541,19 +7481,9 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7568,22 +7498,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126367410</v>
+        <v>126022278</v>
       </c>
       <c r="B67" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7591,42 +7521,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426857</v>
+        <v>426859</v>
       </c>
       <c r="R67" t="n">
-        <v>6800108</v>
+        <v>6799862</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7650,22 +7575,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7680,22 +7595,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126367744</v>
+        <v>126022277</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7703,34 +7618,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426922</v>
+        <v>426835</v>
       </c>
       <c r="R68" t="n">
-        <v>6800077</v>
+        <v>6799747</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7757,22 +7672,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7787,22 +7692,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126369415</v>
+        <v>126368288</v>
       </c>
       <c r="B69" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7810,21 +7715,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7834,10 +7739,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426825</v>
+        <v>426887</v>
       </c>
       <c r="R69" t="n">
-        <v>6799839</v>
+        <v>6800029</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7906,10 +7811,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126367828</v>
+        <v>126368051</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7917,21 +7822,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7941,10 +7846,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426882</v>
+        <v>426857</v>
       </c>
       <c r="R70" t="n">
-        <v>6800101</v>
+        <v>6800079</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8013,10 +7918,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126369426</v>
+        <v>126367203</v>
       </c>
       <c r="B71" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8024,21 +7929,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8048,10 +7953,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426825</v>
+        <v>426916</v>
       </c>
       <c r="R71" t="n">
-        <v>6799839</v>
+        <v>6800140</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8120,10 +8025,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126369749</v>
+        <v>126369422</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8131,21 +8036,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8155,13 +8060,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426870</v>
+        <v>426825</v>
       </c>
       <c r="R72" t="n">
-        <v>6799878</v>
+        <v>6799839</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8201,11 +8106,6 @@
       <c r="AB72" t="inlineStr">
         <is>
           <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8232,10 +8132,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126367862</v>
+        <v>126368375</v>
       </c>
       <c r="B73" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8243,21 +8143,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8267,10 +8167,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426869</v>
+        <v>426857</v>
       </c>
       <c r="R73" t="n">
-        <v>6800102</v>
+        <v>6800079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8336,6 +8236,1659 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126367784</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>426922</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6800077</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126369323</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126367410</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>426857</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6800108</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126369415</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126367744</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>426922</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6800077</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126367828</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>426882</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6800101</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126369426</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>426825</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6799839</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126369749</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>426870</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6799878</v>
+      </c>
+      <c r="S81" t="n">
+        <v>50</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126367862</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91262</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Billingstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>426869</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6800102</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126377486</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>426862</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6799864</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126377484</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>426888</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6799853</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126377417</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>426848</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6799859</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126377483</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>426873</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6799767</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126377485</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>426896</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6799881</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126377482</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>426864</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6799746</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126377436</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>426835</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6799846</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126377440</v>
+        <v>126407577</v>
       </c>
       <c r="B31" t="n">
-        <v>78736</v>
+        <v>75072</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3734,37 +3734,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426874</v>
+        <v>426608</v>
       </c>
       <c r="R31" t="n">
-        <v>6799673</v>
+        <v>6799647</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,39 +3794,50 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126022279</v>
+        <v>126377440</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,37 +3845,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426702</v>
+        <v>426874</v>
       </c>
       <c r="R32" t="n">
-        <v>6799828</v>
+        <v>6799673</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3885,12 +3899,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3905,19 +3919,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126022280</v>
+        <v>126022279</v>
       </c>
       <c r="B33" t="n">
         <v>78977</v>
@@ -3952,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426740</v>
+        <v>426702</v>
       </c>
       <c r="R33" t="n">
-        <v>6799743</v>
+        <v>6799828</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4014,10 +4028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126369226</v>
+        <v>126022280</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,34 +4039,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426795</v>
+        <v>426740</v>
       </c>
       <c r="R34" t="n">
-        <v>6799834</v>
+        <v>6799743</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4079,22 +4093,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4109,22 +4113,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126366267</v>
+        <v>126369226</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4132,37 +4136,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426742</v>
+        <v>426795</v>
       </c>
       <c r="R35" t="n">
-        <v>6799734</v>
+        <v>6799834</v>
       </c>
       <c r="S35" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4201,7 +4205,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,22 +4220,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126368547</v>
+        <v>126366267</v>
       </c>
       <c r="B36" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4239,37 +4243,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426811</v>
+        <v>426742</v>
       </c>
       <c r="R36" t="n">
-        <v>6799987</v>
+        <v>6799734</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4298,7 +4302,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4308,7 +4312,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4323,22 +4327,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126369220</v>
+        <v>126368547</v>
       </c>
       <c r="B37" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4350,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,10 +4374,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426795</v>
+        <v>426811</v>
       </c>
       <c r="R37" t="n">
-        <v>6799834</v>
+        <v>6799987</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4442,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126368672</v>
+        <v>126369220</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4453,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4477,10 +4481,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426807</v>
+        <v>426795</v>
       </c>
       <c r="R38" t="n">
-        <v>6799965</v>
+        <v>6799834</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4549,7 +4553,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126369239</v>
+        <v>126368672</v>
       </c>
       <c r="B39" t="n">
         <v>78977</v>
@@ -4584,10 +4588,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426795</v>
+        <v>426807</v>
       </c>
       <c r="R39" t="n">
-        <v>6799834</v>
+        <v>6799965</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,7 +4660,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126366191</v>
+        <v>126369239</v>
       </c>
       <c r="B40" t="n">
         <v>78977</v>
@@ -4687,17 +4691,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426755</v>
+        <v>426795</v>
       </c>
       <c r="R40" t="n">
-        <v>6799784</v>
+        <v>6799834</v>
       </c>
       <c r="S40" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4726,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4751,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126364937</v>
+        <v>126366191</v>
       </c>
       <c r="B41" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,21 +4778,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4798,13 +4802,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426794</v>
+        <v>426755</v>
       </c>
       <c r="R41" t="n">
-        <v>6799823</v>
+        <v>6799784</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4833,7 +4837,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4843,7 +4847,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4858,22 +4862,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126365001</v>
+        <v>126364937</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4881,21 +4885,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4908,7 +4912,7 @@
         <v>426794</v>
       </c>
       <c r="R42" t="n">
-        <v>6799824</v>
+        <v>6799823</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4940,7 +4944,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4950,7 +4954,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4977,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126369140</v>
+        <v>126365001</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4988,37 +4992,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426770</v>
+        <v>426794</v>
       </c>
       <c r="R43" t="n">
-        <v>6799835</v>
+        <v>6799824</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5047,7 +5051,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5057,7 +5061,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5072,22 +5076,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126364974</v>
+        <v>126369140</v>
       </c>
       <c r="B44" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5095,37 +5099,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426794</v>
+        <v>426770</v>
       </c>
       <c r="R44" t="n">
-        <v>6799824</v>
+        <v>6799835</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5154,7 +5158,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5164,7 +5168,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5179,22 +5183,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126368623</v>
+        <v>126364974</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5202,37 +5206,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426819</v>
+        <v>426794</v>
       </c>
       <c r="R45" t="n">
-        <v>6799948</v>
+        <v>6799824</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5261,7 +5265,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5271,7 +5275,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5286,22 +5290,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126365729</v>
+        <v>126368623</v>
       </c>
       <c r="B46" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5309,37 +5313,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426740</v>
+        <v>426819</v>
       </c>
       <c r="R46" t="n">
-        <v>6799823</v>
+        <v>6799948</v>
       </c>
       <c r="S46" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5368,7 +5372,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5378,7 +5382,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5393,44 +5397,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126365161</v>
+        <v>126365729</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>79566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,13 +5444,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426764</v>
+        <v>426740</v>
       </c>
       <c r="R47" t="n">
-        <v>6799876</v>
+        <v>6799823</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5475,7 +5479,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5485,7 +5489,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5500,60 +5504,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126368738</v>
+        <v>126365161</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426799</v>
+        <v>426764</v>
       </c>
       <c r="R48" t="n">
-        <v>6799946</v>
+        <v>6799876</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5582,7 +5586,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5592,7 +5596,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5607,22 +5611,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126366027</v>
+        <v>126368738</v>
       </c>
       <c r="B49" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5630,37 +5634,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426740</v>
+        <v>426799</v>
       </c>
       <c r="R49" t="n">
-        <v>6799823</v>
+        <v>6799946</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5689,7 +5693,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5699,7 +5703,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5714,22 +5718,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126368886</v>
+        <v>126366027</v>
       </c>
       <c r="B50" t="n">
-        <v>78978</v>
+        <v>79595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5737,37 +5741,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426786</v>
+        <v>426740</v>
       </c>
       <c r="R50" t="n">
-        <v>6799905</v>
+        <v>6799823</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5796,7 +5800,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5806,12 +5810,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5826,22 +5825,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126369595</v>
+        <v>126368886</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5849,16 +5848,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5873,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426797</v>
+        <v>426786</v>
       </c>
       <c r="R51" t="n">
-        <v>6799865</v>
+        <v>6799905</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5919,6 +5918,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,10 +5949,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126365589</v>
+        <v>126369595</v>
       </c>
       <c r="B52" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5956,37 +5960,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426715</v>
+        <v>426797</v>
       </c>
       <c r="R52" t="n">
-        <v>6799803</v>
+        <v>6799865</v>
       </c>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6015,7 +6019,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6025,7 +6029,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,19 +6044,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126366141</v>
+        <v>126365589</v>
       </c>
       <c r="B53" t="n">
         <v>79595</v>
@@ -6087,13 +6091,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426755</v>
+        <v>426715</v>
       </c>
       <c r="R53" t="n">
-        <v>6799784</v>
+        <v>6799803</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6122,7 +6126,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6132,7 +6136,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6159,10 +6163,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126364655</v>
+        <v>126366141</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6170,21 +6174,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6194,13 +6198,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426686</v>
+        <v>426755</v>
       </c>
       <c r="R54" t="n">
-        <v>6799727</v>
+        <v>6799784</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6229,7 +6233,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6239,7 +6243,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6254,22 +6258,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126369214</v>
+        <v>126364655</v>
       </c>
       <c r="B55" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6277,37 +6281,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426795</v>
+        <v>426686</v>
       </c>
       <c r="R55" t="n">
-        <v>6799834</v>
+        <v>6799727</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6336,7 +6340,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6346,7 +6350,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,22 +6365,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126369047</v>
+        <v>126369214</v>
       </c>
       <c r="B56" t="n">
-        <v>75072</v>
+        <v>78735</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6384,21 +6388,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,10 +6412,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426765</v>
+        <v>426795</v>
       </c>
       <c r="R56" t="n">
-        <v>6799867</v>
+        <v>6799834</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6454,11 +6458,6 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,53 +6484,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126368420</v>
+        <v>126369047</v>
       </c>
       <c r="B57" t="n">
-        <v>58025</v>
+        <v>75072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426822</v>
+        <v>426765</v>
       </c>
       <c r="R57" t="n">
-        <v>6800068</v>
+        <v>6799867</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6571,6 +6565,11 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6597,48 +6596,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126366000</v>
+        <v>126368420</v>
       </c>
       <c r="B58" t="n">
-        <v>78735</v>
+        <v>58025</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426787</v>
+        <v>426822</v>
       </c>
       <c r="R58" t="n">
-        <v>6799803</v>
+        <v>6800068</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6667,7 +6671,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6677,7 +6681,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6692,22 +6696,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126365552</v>
+        <v>126366000</v>
       </c>
       <c r="B59" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6715,21 +6719,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6739,10 +6743,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426713</v>
+        <v>426787</v>
       </c>
       <c r="R59" t="n">
-        <v>6799823</v>
+        <v>6799803</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6774,7 +6778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6811,10 +6815,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126365510</v>
+        <v>126365552</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6822,21 +6826,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6846,10 +6850,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426702</v>
+        <v>426713</v>
       </c>
       <c r="R60" t="n">
-        <v>6799810</v>
+        <v>6799823</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6881,7 +6885,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6891,7 +6895,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6918,7 +6922,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126365473</v>
+        <v>126365510</v>
       </c>
       <c r="B61" t="n">
         <v>78977</v>
@@ -6953,13 +6957,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426701</v>
+        <v>426702</v>
       </c>
       <c r="R61" t="n">
-        <v>6799809</v>
+        <v>6799810</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6988,7 +6992,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6998,7 +7002,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7025,10 +7029,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126377418</v>
+        <v>126365473</v>
       </c>
       <c r="B62" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7036,37 +7040,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426816</v>
+        <v>426701</v>
       </c>
       <c r="R62" t="n">
-        <v>6799846</v>
+        <v>6799809</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7093,9 +7097,19 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7110,22 +7124,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126377462</v>
+        <v>126377418</v>
       </c>
       <c r="B63" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7133,21 +7147,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7157,10 +7171,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426794</v>
+        <v>426816</v>
       </c>
       <c r="R63" t="n">
-        <v>6799832</v>
+        <v>6799846</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7219,10 +7233,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126377487</v>
+        <v>126377462</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7230,21 +7244,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7254,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426795</v>
+        <v>426794</v>
       </c>
       <c r="R64" t="n">
-        <v>6799828</v>
+        <v>6799832</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7316,10 +7330,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126377441</v>
+        <v>126377487</v>
       </c>
       <c r="B65" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,21 +7341,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7351,10 +7365,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426816</v>
+        <v>426795</v>
       </c>
       <c r="R65" t="n">
-        <v>6799846</v>
+        <v>6799828</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7413,10 +7427,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126377461</v>
+        <v>126377441</v>
       </c>
       <c r="B66" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7424,21 +7438,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7510,10 +7524,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126022278</v>
+        <v>126377461</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7521,37 +7535,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426859</v>
+        <v>426816</v>
       </c>
       <c r="R67" t="n">
-        <v>6799862</v>
+        <v>6799846</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7575,12 +7589,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7595,22 +7609,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126022277</v>
+        <v>126365268</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7618,34 +7632,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mjölkbäcken norra, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426835</v>
+        <v>426707</v>
       </c>
       <c r="R68" t="n">
-        <v>6799747</v>
+        <v>6799772</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7672,12 +7686,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7692,19 +7716,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126368288</v>
+        <v>126022278</v>
       </c>
       <c r="B69" t="n">
         <v>78977</v>
@@ -7735,14 +7759,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426887</v>
+        <v>426859</v>
       </c>
       <c r="R69" t="n">
-        <v>6800029</v>
+        <v>6799862</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7769,22 +7793,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7799,22 +7813,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126368051</v>
+        <v>126022277</v>
       </c>
       <c r="B70" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7822,34 +7836,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Mjölkbäcken norra, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426857</v>
+        <v>426835</v>
       </c>
       <c r="R70" t="n">
-        <v>6800079</v>
+        <v>6799747</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7876,22 +7890,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>17:46</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7906,19 +7910,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126367203</v>
+        <v>126368288</v>
       </c>
       <c r="B71" t="n">
         <v>78977</v>
@@ -7953,10 +7957,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426916</v>
+        <v>426887</v>
       </c>
       <c r="R71" t="n">
-        <v>6800140</v>
+        <v>6800029</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8025,10 +8029,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126369422</v>
+        <v>126368051</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>75072</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8036,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8060,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426825</v>
+        <v>426857</v>
       </c>
       <c r="R72" t="n">
-        <v>6799839</v>
+        <v>6800079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8132,7 +8136,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126368375</v>
+        <v>126367203</v>
       </c>
       <c r="B73" t="n">
         <v>78977</v>
@@ -8167,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426857</v>
+        <v>426916</v>
       </c>
       <c r="R73" t="n">
-        <v>6800079</v>
+        <v>6800140</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8239,10 +8243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126367784</v>
+        <v>126369422</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8250,21 +8254,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8274,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426922</v>
+        <v>426825</v>
       </c>
       <c r="R74" t="n">
-        <v>6800077</v>
+        <v>6799839</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8346,7 +8350,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126369323</v>
+        <v>126368375</v>
       </c>
       <c r="B75" t="n">
         <v>78977</v>
@@ -8381,10 +8385,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426825</v>
+        <v>426857</v>
       </c>
       <c r="R75" t="n">
-        <v>6799839</v>
+        <v>6800079</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8453,10 +8457,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126367410</v>
+        <v>126367784</v>
       </c>
       <c r="B76" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8464,42 +8468,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426857</v>
+        <v>426922</v>
       </c>
       <c r="R76" t="n">
-        <v>6800108</v>
+        <v>6800077</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8565,10 +8564,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126369415</v>
+        <v>126369323</v>
       </c>
       <c r="B77" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8576,21 +8575,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8672,10 +8671,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126367744</v>
+        <v>126367410</v>
       </c>
       <c r="B78" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8683,37 +8682,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426922</v>
+        <v>426857</v>
       </c>
       <c r="R78" t="n">
-        <v>6800077</v>
+        <v>6800108</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8779,10 +8783,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126367828</v>
+        <v>126367744</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8790,21 +8794,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8814,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426882</v>
+        <v>426922</v>
       </c>
       <c r="R79" t="n">
-        <v>6800101</v>
+        <v>6800077</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8886,10 +8890,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126369426</v>
+        <v>126369415</v>
       </c>
       <c r="B80" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8897,21 +8901,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8993,7 +8997,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126369749</v>
+        <v>126367828</v>
       </c>
       <c r="B81" t="n">
         <v>78977</v>
@@ -9028,13 +9032,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426870</v>
+        <v>426882</v>
       </c>
       <c r="R81" t="n">
-        <v>6799878</v>
+        <v>6800101</v>
       </c>
       <c r="S81" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9074,11 +9078,6 @@
       <c r="AB81" t="inlineStr">
         <is>
           <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9105,10 +9104,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126367862</v>
+        <v>126369426</v>
       </c>
       <c r="B82" t="n">
-        <v>91262</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9116,21 +9115,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9140,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426869</v>
+        <v>426825</v>
       </c>
       <c r="R82" t="n">
-        <v>6800102</v>
+        <v>6799839</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9212,7 +9211,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126377486</v>
+        <v>126369749</v>
       </c>
       <c r="B83" t="n">
         <v>78977</v>
@@ -9243,17 +9242,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426862</v>
+        <v>426870</v>
       </c>
       <c r="R83" t="n">
-        <v>6799864</v>
+        <v>6799878</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9280,9 +9279,24 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9297,22 +9311,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126377484</v>
+        <v>126367862</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>91262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9320,37 +9334,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426888</v>
+        <v>426869</v>
       </c>
       <c r="R84" t="n">
-        <v>6799853</v>
+        <v>6800102</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9377,9 +9391,19 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9394,22 +9418,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126377417</v>
+        <v>126377486</v>
       </c>
       <c r="B85" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9417,21 +9441,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9441,10 +9465,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>426848</v>
+        <v>426862</v>
       </c>
       <c r="R85" t="n">
-        <v>6799859</v>
+        <v>6799864</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9503,7 +9527,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126377483</v>
+        <v>126377484</v>
       </c>
       <c r="B86" t="n">
         <v>78977</v>
@@ -9538,10 +9562,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>426873</v>
+        <v>426888</v>
       </c>
       <c r="R86" t="n">
-        <v>6799767</v>
+        <v>6799853</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9600,10 +9624,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126377485</v>
+        <v>126377417</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,21 +9635,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9635,10 +9659,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426896</v>
+        <v>426848</v>
       </c>
       <c r="R87" t="n">
-        <v>6799881</v>
+        <v>6799859</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9697,7 +9721,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126377482</v>
+        <v>126377483</v>
       </c>
       <c r="B88" t="n">
         <v>78977</v>
@@ -9732,10 +9756,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426864</v>
+        <v>426873</v>
       </c>
       <c r="R88" t="n">
-        <v>6799746</v>
+        <v>6799767</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9794,10 +9818,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126377436</v>
+        <v>126377485</v>
       </c>
       <c r="B89" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9805,21 +9829,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9829,10 +9853,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>426835</v>
+        <v>426896</v>
       </c>
       <c r="R89" t="n">
-        <v>6799846</v>
+        <v>6799881</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -9873,7 +9897,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9889,6 +9912,201 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126377482</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>426864</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6799746</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126377436</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>426835</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6799846</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -5409,32 +5409,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126365729</v>
+        <v>126365161</v>
       </c>
       <c r="B47" t="n">
-        <v>79566</v>
+        <v>98269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426740</v>
+        <v>426764</v>
       </c>
       <c r="R47" t="n">
-        <v>6799823</v>
+        <v>6799876</v>
       </c>
       <c r="S47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,44 +5504,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126365161</v>
+        <v>126365729</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>79566</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426764</v>
+        <v>426740</v>
       </c>
       <c r="R48" t="n">
-        <v>6799876</v>
+        <v>6799823</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5611,12 +5611,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126367744</v>
+        <v>126369415</v>
       </c>
       <c r="B79" t="n">
-        <v>79566</v>
+        <v>78735</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426922</v>
+        <v>426825</v>
       </c>
       <c r="R79" t="n">
-        <v>6800077</v>
+        <v>6799839</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126369415</v>
+        <v>126367744</v>
       </c>
       <c r="B80" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426825</v>
+        <v>426922</v>
       </c>
       <c r="R80" t="n">
-        <v>6799839</v>
+        <v>6800077</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -5409,32 +5409,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126365161</v>
+        <v>126365729</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>79566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426764</v>
+        <v>426740</v>
       </c>
       <c r="R47" t="n">
-        <v>6799876</v>
+        <v>6799823</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,44 +5504,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126365729</v>
+        <v>126365161</v>
       </c>
       <c r="B48" t="n">
-        <v>79566</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426740</v>
+        <v>426764</v>
       </c>
       <c r="R48" t="n">
-        <v>6799823</v>
+        <v>6799876</v>
       </c>
       <c r="S48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5611,12 +5611,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126367288</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126367607</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126367628</v>
+        <v>126367690</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126367690</v>
+        <v>126367628</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>126363419</v>
       </c>
       <c r="B6" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>126363493</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>126363538</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>126363391</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>126363342</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>126022276</v>
       </c>
       <c r="B11" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126022272</v>
       </c>
       <c r="B12" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>126022273</v>
       </c>
       <c r="B13" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>126022281</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>126364297</v>
       </c>
       <c r="B15" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>126364904</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>126365078</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>126365181</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126363871</v>
+        <v>126364869</v>
       </c>
       <c r="B19" t="n">
-        <v>75072</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,37 +2475,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426618</v>
+        <v>426638</v>
       </c>
       <c r="R19" t="n">
-        <v>6799683</v>
+        <v>6799643</v>
       </c>
       <c r="S19" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2559,22 +2559,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126364869</v>
+        <v>126364460</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426638</v>
+        <v>426590</v>
       </c>
       <c r="R20" t="n">
-        <v>6799643</v>
+        <v>6799619</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126364460</v>
+        <v>126363871</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>75075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,37 +2689,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426590</v>
+        <v>426618</v>
       </c>
       <c r="R21" t="n">
-        <v>6799619</v>
+        <v>6799683</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2773,12 +2773,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
         <v>126364417</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>126364611</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>126364842</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>126365310</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>126364814</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>126365592</v>
       </c>
       <c r="B27" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>126377439</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>126377460</v>
       </c>
       <c r="B29" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>126377488</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>126407577</v>
       </c>
       <c r="B31" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>126377440</v>
       </c>
       <c r="B32" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>126022279</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>126022280</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126369226</v>
+        <v>126366267</v>
       </c>
       <c r="B35" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4136,37 +4136,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426795</v>
+        <v>426742</v>
       </c>
       <c r="R35" t="n">
-        <v>6799834</v>
+        <v>6799734</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4220,22 +4220,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126366267</v>
+        <v>126369226</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4243,37 +4243,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426742</v>
+        <v>426795</v>
       </c>
       <c r="R36" t="n">
-        <v>6799734</v>
+        <v>6799834</v>
       </c>
       <c r="S36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4327,12 +4327,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4342,7 +4342,7 @@
         <v>126368547</v>
       </c>
       <c r="B37" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126369220</v>
       </c>
       <c r="B38" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>126368672</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>126369239</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>126366191</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>126364937</v>
       </c>
       <c r="B42" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>126365001</v>
       </c>
       <c r="B43" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>126369140</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126364974</v>
+        <v>126368623</v>
       </c>
       <c r="B45" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5206,37 +5206,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426794</v>
+        <v>426819</v>
       </c>
       <c r="R45" t="n">
-        <v>6799824</v>
+        <v>6799948</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5290,22 +5290,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126368623</v>
+        <v>126364974</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,37 +5313,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426819</v>
+        <v>426794</v>
       </c>
       <c r="R46" t="n">
-        <v>6799948</v>
+        <v>6799824</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5397,44 +5397,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126365729</v>
+        <v>126365161</v>
       </c>
       <c r="B47" t="n">
-        <v>79566</v>
+        <v>98278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426740</v>
+        <v>426764</v>
       </c>
       <c r="R47" t="n">
-        <v>6799823</v>
+        <v>6799876</v>
       </c>
       <c r="S47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,44 +5504,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126365161</v>
+        <v>126365729</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>79569</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426764</v>
+        <v>426740</v>
       </c>
       <c r="R48" t="n">
-        <v>6799876</v>
+        <v>6799823</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5611,12 +5611,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5626,7 +5626,7 @@
         <v>126368738</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>126366027</v>
       </c>
       <c r="B50" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>126368886</v>
       </c>
       <c r="B51" t="n">
-        <v>78978</v>
+        <v>78981</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>126369595</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>126365589</v>
       </c>
       <c r="B53" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>126366141</v>
       </c>
       <c r="B54" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>126364655</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6377,10 +6377,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126369214</v>
+        <v>126369047</v>
       </c>
       <c r="B56" t="n">
-        <v>78735</v>
+        <v>75075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6388,21 +6388,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426795</v>
+        <v>426765</v>
       </c>
       <c r="R56" t="n">
-        <v>6799834</v>
+        <v>6799867</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6458,6 +6458,11 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6484,10 +6489,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126369047</v>
+        <v>126369214</v>
       </c>
       <c r="B57" t="n">
-        <v>75072</v>
+        <v>78738</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6495,21 +6500,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426765</v>
+        <v>426795</v>
       </c>
       <c r="R57" t="n">
-        <v>6799867</v>
+        <v>6799834</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6565,11 +6570,6 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav med miljöbilder för området vid bäcken.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6599,7 +6599,7 @@
         <v>126368420</v>
       </c>
       <c r="B58" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>126366000</v>
       </c>
       <c r="B59" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126365552</v>
+        <v>126365510</v>
       </c>
       <c r="B60" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6826,21 +6826,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426713</v>
+        <v>426702</v>
       </c>
       <c r="R60" t="n">
-        <v>6799823</v>
+        <v>6799810</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6922,10 +6922,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126365510</v>
+        <v>126365552</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426702</v>
+        <v>426713</v>
       </c>
       <c r="R61" t="n">
-        <v>6799810</v>
+        <v>6799823</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7032,7 +7032,7 @@
         <v>126365473</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>126377418</v>
       </c>
       <c r="B63" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126377462</v>
+        <v>126377487</v>
       </c>
       <c r="B64" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7244,21 +7244,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426794</v>
+        <v>426795</v>
       </c>
       <c r="R64" t="n">
-        <v>6799832</v>
+        <v>6799828</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7330,10 +7330,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126377487</v>
+        <v>126377462</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,21 +7341,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426795</v>
+        <v>426794</v>
       </c>
       <c r="R65" t="n">
-        <v>6799828</v>
+        <v>6799832</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7430,7 +7430,7 @@
         <v>126377441</v>
       </c>
       <c r="B66" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>126377461</v>
       </c>
       <c r="B67" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>126365268</v>
       </c>
       <c r="B68" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>126022278</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>126022277</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>126368288</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126368051</v>
+        <v>126369422</v>
       </c>
       <c r="B72" t="n">
-        <v>75072</v>
+        <v>78739</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426857</v>
+        <v>426825</v>
       </c>
       <c r="R72" t="n">
-        <v>6800079</v>
+        <v>6799839</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126367203</v>
+        <v>126368051</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>75075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426916</v>
+        <v>426857</v>
       </c>
       <c r="R73" t="n">
-        <v>6800140</v>
+        <v>6800079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126369422</v>
+        <v>126367203</v>
       </c>
       <c r="B74" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8254,21 +8254,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426825</v>
+        <v>426916</v>
       </c>
       <c r="R74" t="n">
-        <v>6799839</v>
+        <v>6800140</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8353,7 +8353,7 @@
         <v>126368375</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>126367784</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>126369323</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>126367410</v>
       </c>
       <c r="B78" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>126369415</v>
       </c>
       <c r="B79" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>126367744</v>
       </c>
       <c r="B80" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>126367828</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>126369426</v>
       </c>
       <c r="B82" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>126369749</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>126367862</v>
       </c>
       <c r="B84" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>126377486</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>126377484</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>126377417</v>
       </c>
       <c r="B87" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>126377483</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>126377485</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>126377482</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>126377436</v>
       </c>
       <c r="B91" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126367690</v>
+        <v>126367628</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126367628</v>
+        <v>126367690</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126369422</v>
+        <v>126368051</v>
       </c>
       <c r="B72" t="n">
-        <v>78739</v>
+        <v>75075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426825</v>
+        <v>426857</v>
       </c>
       <c r="R72" t="n">
-        <v>6799839</v>
+        <v>6800079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126368051</v>
+        <v>126367203</v>
       </c>
       <c r="B73" t="n">
-        <v>75075</v>
+        <v>78980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426857</v>
+        <v>426916</v>
       </c>
       <c r="R73" t="n">
-        <v>6800079</v>
+        <v>6800140</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126367203</v>
+        <v>126369422</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8254,21 +8254,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426916</v>
+        <v>426825</v>
       </c>
       <c r="R74" t="n">
-        <v>6800140</v>
+        <v>6799839</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126369415</v>
+        <v>126367744</v>
       </c>
       <c r="B79" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426825</v>
+        <v>426922</v>
       </c>
       <c r="R79" t="n">
-        <v>6799839</v>
+        <v>6800077</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126367744</v>
+        <v>126369415</v>
       </c>
       <c r="B80" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426922</v>
+        <v>426825</v>
       </c>
       <c r="R80" t="n">
-        <v>6800077</v>
+        <v>6799839</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126364460</v>
+        <v>126363871</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>75075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,37 +2582,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426590</v>
+        <v>426618</v>
       </c>
       <c r="R20" t="n">
-        <v>6799619</v>
+        <v>6799683</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,22 +2666,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126363871</v>
+        <v>126364460</v>
       </c>
       <c r="B21" t="n">
-        <v>75075</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,37 +2689,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426618</v>
+        <v>426590</v>
       </c>
       <c r="R21" t="n">
-        <v>6799683</v>
+        <v>6799619</v>
       </c>
       <c r="S21" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2773,12 +2773,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126364842</v>
+        <v>126365310</v>
       </c>
       <c r="B24" t="n">
         <v>78980</v>
@@ -3034,13 +3034,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426643</v>
+        <v>426696</v>
       </c>
       <c r="R24" t="n">
-        <v>6799654</v>
+        <v>6799616</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126365310</v>
+        <v>126364842</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -3141,13 +3146,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426696</v>
+        <v>426643</v>
       </c>
       <c r="R25" t="n">
-        <v>6799616</v>
+        <v>6799654</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3176,7 +3181,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,12 +3191,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4660,7 +4660,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126369239</v>
+        <v>126366191</v>
       </c>
       <c r="B40" t="n">
         <v>78980</v>
@@ -4691,17 +4691,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426795</v>
+        <v>426755</v>
       </c>
       <c r="R40" t="n">
-        <v>6799834</v>
+        <v>6799784</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,19 +4755,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126366191</v>
+        <v>126369239</v>
       </c>
       <c r="B41" t="n">
         <v>78980</v>
@@ -4798,17 +4798,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426755</v>
+        <v>426795</v>
       </c>
       <c r="R41" t="n">
-        <v>6799784</v>
+        <v>6799834</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4862,12 +4862,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126369140</v>
+        <v>126364974</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5099,37 +5099,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426770</v>
+        <v>426794</v>
       </c>
       <c r="R44" t="n">
-        <v>6799835</v>
+        <v>6799824</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5183,22 +5183,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126368623</v>
+        <v>126365729</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5206,37 +5206,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426819</v>
+        <v>426740</v>
       </c>
       <c r="R45" t="n">
-        <v>6799948</v>
+        <v>6799823</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5290,22 +5290,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126364974</v>
+        <v>126369140</v>
       </c>
       <c r="B46" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,37 +5313,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426794</v>
+        <v>426770</v>
       </c>
       <c r="R46" t="n">
-        <v>6799824</v>
+        <v>6799835</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5397,60 +5397,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126365161</v>
+        <v>126368623</v>
       </c>
       <c r="B47" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426764</v>
+        <v>426819</v>
       </c>
       <c r="R47" t="n">
-        <v>6799876</v>
+        <v>6799948</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,44 +5504,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126365729</v>
+        <v>126365161</v>
       </c>
       <c r="B48" t="n">
-        <v>79569</v>
+        <v>98278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426740</v>
+        <v>426764</v>
       </c>
       <c r="R48" t="n">
-        <v>6799823</v>
+        <v>6799876</v>
       </c>
       <c r="S48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5611,12 +5611,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126364655</v>
+        <v>126369214</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6281,37 +6281,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426686</v>
+        <v>426795</v>
       </c>
       <c r="R55" t="n">
-        <v>6799727</v>
+        <v>6799834</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6365,12 +6365,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6489,10 +6489,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126369214</v>
+        <v>126364655</v>
       </c>
       <c r="B57" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6500,37 +6500,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426795</v>
+        <v>426686</v>
       </c>
       <c r="R57" t="n">
-        <v>6799834</v>
+        <v>6799727</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6584,12 +6584,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126365510</v>
+        <v>126365552</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6826,21 +6826,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426702</v>
+        <v>426713</v>
       </c>
       <c r="R60" t="n">
-        <v>6799810</v>
+        <v>6799823</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6922,10 +6922,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126365552</v>
+        <v>126365510</v>
       </c>
       <c r="B61" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426713</v>
+        <v>426702</v>
       </c>
       <c r="R61" t="n">
-        <v>6799823</v>
+        <v>6799810</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7233,10 +7233,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126377487</v>
+        <v>126377462</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7244,21 +7244,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426795</v>
+        <v>426794</v>
       </c>
       <c r="R64" t="n">
-        <v>6799828</v>
+        <v>6799832</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7330,10 +7330,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126377462</v>
+        <v>126377487</v>
       </c>
       <c r="B65" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,21 +7341,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426794</v>
+        <v>426795</v>
       </c>
       <c r="R65" t="n">
-        <v>6799832</v>
+        <v>6799828</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126368051</v>
+        <v>126367203</v>
       </c>
       <c r="B72" t="n">
-        <v>75075</v>
+        <v>78980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426857</v>
+        <v>426916</v>
       </c>
       <c r="R72" t="n">
-        <v>6800079</v>
+        <v>6800140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126367203</v>
+        <v>126369422</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426916</v>
+        <v>426825</v>
       </c>
       <c r="R73" t="n">
-        <v>6800140</v>
+        <v>6799839</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126369422</v>
+        <v>126368051</v>
       </c>
       <c r="B74" t="n">
-        <v>78739</v>
+        <v>75075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8254,21 +8254,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426825</v>
+        <v>426857</v>
       </c>
       <c r="R74" t="n">
-        <v>6799839</v>
+        <v>6800079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -5088,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126364974</v>
+        <v>126365729</v>
       </c>
       <c r="B44" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5099,21 +5099,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426794</v>
+        <v>426740</v>
       </c>
       <c r="R44" t="n">
-        <v>6799824</v>
+        <v>6799823</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5183,22 +5183,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126365729</v>
+        <v>126369140</v>
       </c>
       <c r="B45" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5206,37 +5206,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426740</v>
+        <v>426770</v>
       </c>
       <c r="R45" t="n">
-        <v>6799823</v>
+        <v>6799835</v>
       </c>
       <c r="S45" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5290,19 +5290,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126369140</v>
+        <v>126368623</v>
       </c>
       <c r="B46" t="n">
         <v>78980</v>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426770</v>
+        <v>426819</v>
       </c>
       <c r="R46" t="n">
-        <v>6799835</v>
+        <v>6799948</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5409,10 +5409,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126368623</v>
+        <v>126364974</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5420,37 +5420,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Billingstjärnarna, Dlr</t>
+          <t>Billingstjärnarna, Billingstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426819</v>
+        <v>426794</v>
       </c>
       <c r="R47" t="n">
-        <v>6799948</v>
+        <v>6799824</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,12 +5504,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126367203</v>
+        <v>126368051</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>75075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426916</v>
+        <v>426857</v>
       </c>
       <c r="R72" t="n">
-        <v>6800140</v>
+        <v>6800079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126369422</v>
+        <v>126367203</v>
       </c>
       <c r="B73" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426825</v>
+        <v>426916</v>
       </c>
       <c r="R73" t="n">
-        <v>6799839</v>
+        <v>6800140</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126368051</v>
+        <v>126369422</v>
       </c>
       <c r="B74" t="n">
-        <v>75075</v>
+        <v>78739</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8254,21 +8254,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426857</v>
+        <v>426825</v>
       </c>
       <c r="R74" t="n">
-        <v>6800079</v>
+        <v>6799839</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126367628</v>
+        <v>126367690</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126367690</v>
+        <v>126367628</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126368051</v>
+        <v>126367203</v>
       </c>
       <c r="B72" t="n">
-        <v>75075</v>
+        <v>78980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426857</v>
+        <v>426916</v>
       </c>
       <c r="R72" t="n">
-        <v>6800079</v>
+        <v>6800140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126367203</v>
+        <v>126369422</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426916</v>
+        <v>426825</v>
       </c>
       <c r="R73" t="n">
-        <v>6800140</v>
+        <v>6799839</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126369422</v>
+        <v>126368051</v>
       </c>
       <c r="B74" t="n">
-        <v>78739</v>
+        <v>75075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8254,21 +8254,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426825</v>
+        <v>426857</v>
       </c>
       <c r="R74" t="n">
-        <v>6799839</v>
+        <v>6800079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -7139,7 +7139,7 @@
         <v>126377418</v>
       </c>
       <c r="B63" t="n">
-        <v>79598</v>
+        <v>79706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7165,6 +7165,9 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rytterbygget, Dlr</t>
@@ -9627,7 +9630,7 @@
         <v>126377417</v>
       </c>
       <c r="B87" t="n">
-        <v>79598</v>
+        <v>79706</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9653,6 +9656,9 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rytterbygget, Dlr</t>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -7139,7 +7139,7 @@
         <v>126377418</v>
       </c>
       <c r="B63" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>126377417</v>
       </c>
       <c r="B87" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -7139,7 +7139,7 @@
         <v>126377418</v>
       </c>
       <c r="B63" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>126377417</v>
       </c>
       <c r="B87" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 29154-2025 artfynd.xlsx
+++ b/artfynd/A 29154-2025 artfynd.xlsx
@@ -7139,7 +7139,7 @@
         <v>126377418</v>
       </c>
       <c r="B63" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>126377417</v>
       </c>
       <c r="B87" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
